--- a/docentes/Avila Coronado Julieta - Estadisticos 20232.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -82,103 +82,112 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>ESPARZA</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DIEGO ANTONIO</t>
   </si>
   <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>ANGELES VALERIA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>CARLOS YAEL</t>
   </si>
   <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
     <t>AARON MIGUEL</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
     <t>AHILY</t>
   </si>
   <si>
     <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -774,16 +783,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.20999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -797,16 +809,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -820,16 +835,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.29000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -843,16 +861,19 @@
         <v>45</v>
       </c>
       <c r="D5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>77.78</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -866,16 +887,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -889,16 +913,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>92.11</v>
+      </c>
+      <c r="H7">
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -954,16 +981,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1015,7 +1042,7 @@
         <v>94.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1032,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>91.11</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1058,16 +1085,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1084,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>94.73999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,16 +1162,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920013</v>
+        <v>22330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1158,22 +1185,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920173</v>
+        <v>21330051920237</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1181,16 +1208,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920237</v>
+        <v>22330051920068</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1204,22 +1231,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>22330051920218</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1227,22 +1254,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920038</v>
+        <v>21330051920053</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1250,16 +1277,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920043</v>
+        <v>22330051920034</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1273,16 +1300,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920049</v>
+        <v>22330051920043</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1296,22 +1323,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920382</v>
+        <v>22330051920098</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1319,16 +1346,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920098</v>
+        <v>22330051920107</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1342,16 +1369,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920100</v>
+        <v>22330051920116</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1365,22 +1392,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920107</v>
+        <v>22330051920059</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1388,24 +1415,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920116</v>
+        <v>22330051920061</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920145</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Avila Coronado Julieta - Estadisticos 20232.xlsx
+++ b/docentes/Avila Coronado Julieta - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,112 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>PRADO</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LUGO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>ANGELES VALERIA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>ANETTE</t>
+    <t>CLAUDIA PAOLA</t>
+  </si>
+  <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>AHILY</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -981,16 +909,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>86.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1007,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3">
-        <v>88.09999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -1033,13 +961,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>94.29000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
         <v>8.300000000000001</v>
@@ -1059,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5">
-        <v>77.78</v>
+        <v>86.67</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1085,16 +1013,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1111,16 +1039,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>92.11</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1162,22 +1090,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920003</v>
+        <v>22330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1185,16 +1113,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920237</v>
+        <v>22330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1208,254 +1136,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920068</v>
+        <v>22330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920218</v>
+        <v>22330051920107</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920053</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920034</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920043</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920098</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920107</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920116</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920059</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920061</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>
